--- a/demo_data/discharge_summaries.xlsx
+++ b/demo_data/discharge_summaries.xlsx
@@ -496,37 +496,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rajesh Singh</t>
+          <t>Rahul Mehta</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CABG</t>
+          <t>Laparoscopic cholecystectomy</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="M2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -559,41 +559,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Priya Joshi</t>
+          <t>Manish Iyer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mastectomy</t>
+          <t>Hip replacement</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr. Sunita Sharma</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Satisfactory</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -622,41 +622,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anita Shah</t>
+          <t>Arjun Sharma</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TURP</t>
+          <t>Hip replacement</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Satisfactory</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arjun Chatterjee</t>
+          <t>Kavita Kumar</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -695,17 +695,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -715,11 +715,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -748,41 +748,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rajesh Bose</t>
+          <t>Nisha Joshi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CABG</t>
+          <t>Hip replacement</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Satisfactory</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -811,41 +811,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rahul Joshi</t>
+          <t>Vikram Iyer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Laminectomy</t>
+          <t>TURP</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="M7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -874,27 +874,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kiran Reddy</t>
+          <t>Sanjay Kumar</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mastectomy</t>
+          <t>CABG</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Vikram Rao</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -904,11 +904,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -937,37 +937,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Suresh Sharma</t>
+          <t>Kavita Dutta</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hysterectomy</t>
+          <t>Hip replacement</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="M9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1000,27 +1000,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sunita Gupta</t>
+          <t>Rajesh Malhotra</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hip replacement</t>
+          <t>TURP</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Priya Mehta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1030,11 +1030,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1063,27 +1063,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deepa Patel</t>
+          <t>Kiran Mehta</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CABG</t>
+          <t>Hysterectomy</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dr. Manish Gupta</t>
+          <t>Dr. Suresh Reddy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1093,11 +1093,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="M11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1126,27 +1126,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Anita Rao</t>
+          <t>Rekha Nair</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hysterectomy</t>
+          <t>TURP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1156,11 +1156,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1189,37 +1189,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vikram Mehta</t>
+          <t>Deepa Kumar</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TURP</t>
+          <t>Caesarean section</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="M13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1252,41 +1252,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Deepa Chatterjee</t>
+          <t>Sanjay Singh</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Laminectomy</t>
+          <t>Total knee replacement</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="M14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1315,41 +1315,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunita Patel</t>
+          <t>Meena Kumar</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Laminectomy</t>
+          <t>Mastectomy</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1378,41 +1378,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Anita Bose</t>
+          <t>Manish Gupta</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TURP</t>
+          <t>Laminectomy</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Manish Gupta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="M16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1441,41 +1441,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sunita Rao</t>
+          <t>Anita Patel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hysterectomy</t>
+          <t>Hip replacement</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Vikram Rao</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Satisfactory</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1504,37 +1504,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vikram Shah</t>
+          <t>Amit Gupta</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hip replacement</t>
+          <t>Mastectomy</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Vikram Rao</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Satisfactory</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sanjay Gupta</t>
+          <t>Suresh Sharma</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Total knee replacement</t>
+          <t>Hip replacement</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1582,26 +1582,26 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1630,41 +1630,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Meena Patel</t>
+          <t>Kavita Rao</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TURP</t>
+          <t>Mastectomy</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Stable</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1693,41 +1693,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Arjun Gupta</t>
+          <t>Vikram Sharma</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Appendectomy</t>
+          <t>CABG</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Satisfactory</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="M21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
